--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 356</t>
+            <t xml:space="preserve">3 569 992</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.77</t>
+            <t xml:space="preserve">56.74</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">460 339</t>
+            <t xml:space="preserve">461 060</t>
           </r>
         </is>
       </c>
@@ -289,7 +289,7 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">7.32</t>
+            <t xml:space="preserve">7.33</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 620</t>
+            <t xml:space="preserve">143 780</t>
           </r>
         </is>
       </c>
@@ -315,7 +315,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2.28</t>
+            <t xml:space="preserve">2.29</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">779 282</t>
+            <t xml:space="preserve">778 818</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.39</t>
+            <t xml:space="preserve">12.38</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 135 230</t>
+            <t xml:space="preserve">1 134 438</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.05</t>
+            <t xml:space="preserve">18.03</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 368</t>
+            <t xml:space="preserve">545 448</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 838</t>
+            <t xml:space="preserve">309 650</t>
           </r>
         </is>
       </c>
@@ -419,7 +419,7 @@
       <c r="E9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">4.93</t>
+            <t xml:space="preserve">4.92</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 376</t>
+            <t xml:space="preserve">84 561</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 303</t>
+            <t xml:space="preserve">112 237</t>
           </r>
         </is>
       </c>
@@ -471,7 +471,7 @@
       <c r="E11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.79</t>
+            <t xml:space="preserve">1.78</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 578 117</t>
+            <t xml:space="preserve">1 579 554</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.09</t>
+            <t xml:space="preserve">25.11</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 201 357</t>
+            <t xml:space="preserve">1 202 195</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.10</t>
+            <t xml:space="preserve">19.11</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">218 274</t>
+            <t xml:space="preserve">218 736</t>
           </r>
         </is>
       </c>
@@ -549,7 +549,7 @@
       <c r="E14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.47</t>
+            <t xml:space="preserve">3.48</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 826</t>
+            <t xml:space="preserve">57 906</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 672</t>
+            <t xml:space="preserve">32 655</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 032</t>
+            <t xml:space="preserve">40 051</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">981</t>
+            <t xml:space="preserve">982</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 419</t>
+            <t xml:space="preserve">2 423</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 556</t>
+            <t xml:space="preserve">24 606</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 055 596</t>
+            <t xml:space="preserve">1 056 708</t>
           </r>
         </is>
       </c>
@@ -731,7 +731,7 @@
       <c r="E21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16.78</t>
+            <t xml:space="preserve">16.80</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 048</t>
+            <t xml:space="preserve">33 132</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 547</t>
+            <t xml:space="preserve">208 610</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">747 770</t>
+            <t xml:space="preserve">748 717</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.89</t>
+            <t xml:space="preserve">11.90</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 231</t>
+            <t xml:space="preserve">66 249</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 176</t>
+            <t xml:space="preserve">85 480</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.35</t>
+            <t xml:space="preserve">1.36</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 176</t>
+            <t xml:space="preserve">85 480</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.35</t>
+            <t xml:space="preserve">1.36</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46134.32026293967</v>
+        <v>46147.32025572937</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 992</t>
+            <t xml:space="preserve">3 569 632</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.74</t>
+            <t xml:space="preserve">56.71</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">461 060</t>
+            <t xml:space="preserve">461 745</t>
           </r>
         </is>
       </c>
@@ -289,7 +289,7 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">7.33</t>
+            <t xml:space="preserve">7.34</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 780</t>
+            <t xml:space="preserve">143 967</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">778 818</t>
+            <t xml:space="preserve">778 287</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.38</t>
+            <t xml:space="preserve">12.36</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 134 438</t>
+            <t xml:space="preserve">1 133 741</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.03</t>
+            <t xml:space="preserve">18.01</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 448</t>
+            <t xml:space="preserve">545 549</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 650</t>
+            <t xml:space="preserve">309 474</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 561</t>
+            <t xml:space="preserve">84 702</t>
           </r>
         </is>
       </c>
@@ -445,7 +445,7 @@
       <c r="E10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.34</t>
+            <t xml:space="preserve">1.35</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 237</t>
+            <t xml:space="preserve">112 167</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 579 554</t>
+            <t xml:space="preserve">1 581 084</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.11</t>
+            <t xml:space="preserve">25.12</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 202 195</t>
+            <t xml:space="preserve">1 203 089</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">218 736</t>
+            <t xml:space="preserve">219 243</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 906</t>
+            <t xml:space="preserve">57 972</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 655</t>
+            <t xml:space="preserve">32 635</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 051</t>
+            <t xml:space="preserve">40 082</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">982</t>
+            <t xml:space="preserve">981</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 423</t>
+            <t xml:space="preserve">2 433</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 606</t>
+            <t xml:space="preserve">24 649</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 056 708</t>
+            <t xml:space="preserve">1 057 830</t>
           </r>
         </is>
       </c>
@@ -731,7 +731,7 @@
       <c r="E21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16.80</t>
+            <t xml:space="preserve">16.81</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 132</t>
+            <t xml:space="preserve">33 221</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 610</t>
+            <t xml:space="preserve">208 688</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">748 717</t>
+            <t xml:space="preserve">749 658</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.90</t>
+            <t xml:space="preserve">11.91</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 249</t>
+            <t xml:space="preserve">66 263</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 480</t>
+            <t xml:space="preserve">85 767</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 480</t>
+            <t xml:space="preserve">85 767</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46147.32025572937</v>
+        <v>46157.32026042836</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 632</t>
+            <t xml:space="preserve">3 569 586</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">461 745</t>
+            <t xml:space="preserve">461 820</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 967</t>
+            <t xml:space="preserve">143 986</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">778 287</t>
+            <t xml:space="preserve">778 248</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 741</t>
+            <t xml:space="preserve">1 133 653</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 549</t>
+            <t xml:space="preserve">545 553</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 474</t>
+            <t xml:space="preserve">309 446</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 702</t>
+            <t xml:space="preserve">84 722</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 167</t>
+            <t xml:space="preserve">112 158</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 581 084</t>
+            <t xml:space="preserve">1 581 241</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 089</t>
+            <t xml:space="preserve">1 203 178</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 243</t>
+            <t xml:space="preserve">219 301</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 972</t>
+            <t xml:space="preserve">57 981</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 635</t>
+            <t xml:space="preserve">32 632</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 082</t>
+            <t xml:space="preserve">40 080</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 433</t>
+            <t xml:space="preserve">2 435</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 649</t>
+            <t xml:space="preserve">24 653</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 057 830</t>
+            <t xml:space="preserve">1 057 923</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 221</t>
+            <t xml:space="preserve">33 232</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 688</t>
+            <t xml:space="preserve">208 694</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">749 658</t>
+            <t xml:space="preserve">749 731</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 263</t>
+            <t xml:space="preserve">66 266</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 767</t>
+            <t xml:space="preserve">85 790</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 767</t>
+            <t xml:space="preserve">85 790</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46157.32026042836</v>
+        <v>46158.320272615645</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 586</t>
+            <t xml:space="preserve">3 569 587</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">461 820</t>
+            <t xml:space="preserve">461 845</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 986</t>
+            <t xml:space="preserve">143 997</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">778 248</t>
+            <t xml:space="preserve">778 241</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 653</t>
+            <t xml:space="preserve">1 133 619</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 553</t>
+            <t xml:space="preserve">545 567</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 446</t>
+            <t xml:space="preserve">309 442</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 722</t>
+            <t xml:space="preserve">84 728</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 158</t>
+            <t xml:space="preserve">112 148</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 581 241</t>
+            <t xml:space="preserve">1 581 276</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 178</t>
+            <t xml:space="preserve">1 203 192</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 301</t>
+            <t xml:space="preserve">219 315</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 981</t>
+            <t xml:space="preserve">57 979</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 632</t>
+            <t xml:space="preserve">32 630</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 080</t>
+            <t xml:space="preserve">40 084</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 653</t>
+            <t xml:space="preserve">24 660</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 057 923</t>
+            <t xml:space="preserve">1 058 018</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 232</t>
+            <t xml:space="preserve">33 233</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 694</t>
+            <t xml:space="preserve">208 698</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">749 731</t>
+            <t xml:space="preserve">749 813</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 266</t>
+            <t xml:space="preserve">66 274</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 790</t>
+            <t xml:space="preserve">85 834</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 790</t>
+            <t xml:space="preserve">85 834</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46158.320272615645</v>
+        <v>46160.32026665518</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 587</t>
+            <t xml:space="preserve">3 569 453</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.71</t>
+            <t xml:space="preserve">56.70</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">461 845</t>
+            <t xml:space="preserve">462 022</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 997</t>
+            <t xml:space="preserve">144 057</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">778 241</t>
+            <t xml:space="preserve">778 088</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 619</t>
+            <t xml:space="preserve">1 133 439</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.01</t>
+            <t xml:space="preserve">18.00</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 567</t>
+            <t xml:space="preserve">545 574</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 442</t>
+            <t xml:space="preserve">309 406</t>
           </r>
         </is>
       </c>
@@ -419,7 +419,7 @@
       <c r="E9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">4.92</t>
+            <t xml:space="preserve">4.91</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 728</t>
+            <t xml:space="preserve">84 741</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 148</t>
+            <t xml:space="preserve">112 126</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 581 276</t>
+            <t xml:space="preserve">1 581 662</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 192</t>
+            <t xml:space="preserve">1 203 430</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.11</t>
+            <t xml:space="preserve">19.12</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 315</t>
+            <t xml:space="preserve">219 430</t>
           </r>
         </is>
       </c>
@@ -549,7 +549,7 @@
       <c r="E14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.48</t>
+            <t xml:space="preserve">3.49</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 979</t>
+            <t xml:space="preserve">57 989</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 630</t>
+            <t xml:space="preserve">32 627</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 084</t>
+            <t xml:space="preserve">40 094</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">981</t>
+            <t xml:space="preserve">982</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 435</t>
+            <t xml:space="preserve">2 438</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 660</t>
+            <t xml:space="preserve">24 672</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 018</t>
+            <t xml:space="preserve">1 058 253</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 233</t>
+            <t xml:space="preserve">33 255</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 698</t>
+            <t xml:space="preserve">208 716</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">749 813</t>
+            <t xml:space="preserve">749 997</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 274</t>
+            <t xml:space="preserve">66 285</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 834</t>
+            <t xml:space="preserve">85 907</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 834</t>
+            <t xml:space="preserve">85 907</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46160.32026665518</v>
+        <v>46162.32025582157</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 453</t>
+            <t xml:space="preserve">3 569 368</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.70</t>
+            <t xml:space="preserve">56.69</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">462 022</t>
+            <t xml:space="preserve">462 224</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">144 057</t>
+            <t xml:space="preserve">144 081</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">778 088</t>
+            <t xml:space="preserve">777 969</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 439</t>
+            <t xml:space="preserve">1 133 225</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 574</t>
+            <t xml:space="preserve">545 597</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 406</t>
+            <t xml:space="preserve">309 384</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 741</t>
+            <t xml:space="preserve">84 771</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 126</t>
+            <t xml:space="preserve">112 117</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 581 662</t>
+            <t xml:space="preserve">1 582 014</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.12</t>
+            <t xml:space="preserve">25.13</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 430</t>
+            <t xml:space="preserve">1 203 644</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 430</t>
+            <t xml:space="preserve">219 540</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">57 989</t>
+            <t xml:space="preserve">58 006</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 627</t>
+            <t xml:space="preserve">32 631</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 094</t>
+            <t xml:space="preserve">40 098</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">982</t>
+            <t xml:space="preserve">983</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 438</t>
+            <t xml:space="preserve">2 439</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 672</t>
+            <t xml:space="preserve">24 673</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 253</t>
+            <t xml:space="preserve">1 058 474</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 255</t>
+            <t xml:space="preserve">33 263</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 716</t>
+            <t xml:space="preserve">208 731</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">749 997</t>
+            <t xml:space="preserve">750 190</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.91</t>
+            <t xml:space="preserve">11.92</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 285</t>
+            <t xml:space="preserve">66 290</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 907</t>
+            <t xml:space="preserve">85 968</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.36</t>
+            <t xml:space="preserve">1.37</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 907</t>
+            <t xml:space="preserve">85 968</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.36</t>
+            <t xml:space="preserve">1.37</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46162.32025582157</v>
+        <v>46164.32025482645</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 368</t>
+            <t xml:space="preserve">3 569 328</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">462 224</t>
+            <t xml:space="preserve">462 272</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">144 081</t>
+            <t xml:space="preserve">144 098</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">777 969</t>
+            <t xml:space="preserve">777 908</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 225</t>
+            <t xml:space="preserve">1 133 162</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 597</t>
+            <t xml:space="preserve">545 615</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 384</t>
+            <t xml:space="preserve">309 385</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 771</t>
+            <t xml:space="preserve">84 783</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 117</t>
+            <t xml:space="preserve">112 105</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 582 014</t>
+            <t xml:space="preserve">1 582 143</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 644</t>
+            <t xml:space="preserve">1 203 728</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 540</t>
+            <t xml:space="preserve">219 572</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 006</t>
+            <t xml:space="preserve">58 012</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 631</t>
+            <t xml:space="preserve">32 632</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 673</t>
+            <t xml:space="preserve">24 679</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 474</t>
+            <t xml:space="preserve">1 058 581</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 263</t>
+            <t xml:space="preserve">33 276</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 731</t>
+            <t xml:space="preserve">208 736</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 190</t>
+            <t xml:space="preserve">750 272</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 290</t>
+            <t xml:space="preserve">66 297</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 968</t>
+            <t xml:space="preserve">85 977</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 968</t>
+            <t xml:space="preserve">85 977</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46164.32025482645</v>
+        <v>46165.3202618286</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 328</t>
+            <t xml:space="preserve">3 570 136</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.69</t>
+            <t xml:space="preserve">56.70</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">462 272</t>
+            <t xml:space="preserve">463 978</t>
           </r>
         </is>
       </c>
@@ -289,7 +289,7 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">7.34</t>
+            <t xml:space="preserve">7.37</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">144 098</t>
+            <t xml:space="preserve">145 014</t>
           </r>
         </is>
       </c>
@@ -315,7 +315,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2.29</t>
+            <t xml:space="preserve">2.30</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">777 908</t>
+            <t xml:space="preserve">781 149</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.36</t>
+            <t xml:space="preserve">12.41</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 133 162</t>
+            <t xml:space="preserve">1 136 666</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.00</t>
+            <t xml:space="preserve">18.05</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">545 615</t>
+            <t xml:space="preserve">547 039</t>
           </r>
         </is>
       </c>
@@ -393,7 +393,7 @@
       <c r="E8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">8.67</t>
+            <t xml:space="preserve">8.69</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 385</t>
+            <t xml:space="preserve">309 313</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 783</t>
+            <t xml:space="preserve">84 798</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">112 105</t>
+            <t xml:space="preserve">102 179</t>
           </r>
         </is>
       </c>
@@ -471,7 +471,7 @@
       <c r="E11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.78</t>
+            <t xml:space="preserve">1.62</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 582 143</t>
+            <t xml:space="preserve">1 583 623</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.13</t>
+            <t xml:space="preserve">25.15</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 203 728</t>
+            <t xml:space="preserve">1 204 455</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.12</t>
+            <t xml:space="preserve">19.13</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 572</t>
+            <t xml:space="preserve">219 996</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 012</t>
+            <t xml:space="preserve">58 292</t>
           </r>
         </is>
       </c>
@@ -575,7 +575,7 @@
       <c r="E15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">0.92</t>
+            <t xml:space="preserve">0.93</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 632</t>
+            <t xml:space="preserve">32 652</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 098</t>
+            <t xml:space="preserve">40 120</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">983</t>
+            <t xml:space="preserve">984</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 439</t>
+            <t xml:space="preserve">2 438</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 679</t>
+            <t xml:space="preserve">24 686</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 581</t>
+            <t xml:space="preserve">1 058 852</t>
           </r>
         </is>
       </c>
@@ -731,7 +731,7 @@
       <c r="E21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16.81</t>
+            <t xml:space="preserve">16.82</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 276</t>
+            <t xml:space="preserve">33 295</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 736</t>
+            <t xml:space="preserve">208 756</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 272</t>
+            <t xml:space="preserve">750 491</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 297</t>
+            <t xml:space="preserve">66 310</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 977</t>
+            <t xml:space="preserve">84 086</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.37</t>
+            <t xml:space="preserve">1.34</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">85 977</t>
+            <t xml:space="preserve">84 086</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.37</t>
+            <t xml:space="preserve">1.34</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46165.3202618286</v>
+        <v>46169.320276516024</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 136</t>
+            <t xml:space="preserve">3 570 093</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">463 978</t>
+            <t xml:space="preserve">464 046</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 014</t>
+            <t xml:space="preserve">145 035</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">781 149</t>
+            <t xml:space="preserve">781 103</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.41</t>
+            <t xml:space="preserve">12.40</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 666</t>
+            <t xml:space="preserve">1 136 581</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 039</t>
+            <t xml:space="preserve">547 056</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 313</t>
+            <t xml:space="preserve">309 292</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 798</t>
+            <t xml:space="preserve">84 808</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 179</t>
+            <t xml:space="preserve">102 172</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 583 623</t>
+            <t xml:space="preserve">1 583 774</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 455</t>
+            <t xml:space="preserve">1 204 564</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">219 996</t>
+            <t xml:space="preserve">220 036</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 652</t>
+            <t xml:space="preserve">32 648</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 438</t>
+            <t xml:space="preserve">2 439</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 686</t>
+            <t xml:space="preserve">24 691</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 852</t>
+            <t xml:space="preserve">1 058 941</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 295</t>
+            <t xml:space="preserve">33 305</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 756</t>
+            <t xml:space="preserve">208 766</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 491</t>
+            <t xml:space="preserve">750 562</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 310</t>
+            <t xml:space="preserve">66 308</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 086</t>
+            <t xml:space="preserve">84 116</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 086</t>
+            <t xml:space="preserve">84 116</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46169.320276516024</v>
+        <v>46170.3202526737</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 093</t>
+            <t xml:space="preserve">3 570 050</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.70</t>
+            <t xml:space="preserve">56.69</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 046</t>
+            <t xml:space="preserve">464 145</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 035</t>
+            <t xml:space="preserve">145 058</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">781 103</t>
+            <t xml:space="preserve">781 030</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 581</t>
+            <t xml:space="preserve">1 136 492</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 056</t>
+            <t xml:space="preserve">547 073</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 292</t>
+            <t xml:space="preserve">309 271</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 808</t>
+            <t xml:space="preserve">84 811</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 172</t>
+            <t xml:space="preserve">102 170</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 583 774</t>
+            <t xml:space="preserve">1 583 929</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 564</t>
+            <t xml:space="preserve">1 204 667</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">220 036</t>
+            <t xml:space="preserve">220 068</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 292</t>
+            <t xml:space="preserve">58 306</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 648</t>
+            <t xml:space="preserve">32 646</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 120</t>
+            <t xml:space="preserve">40 124</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 439</t>
+            <t xml:space="preserve">2 438</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 691</t>
+            <t xml:space="preserve">24 696</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 058 941</t>
+            <t xml:space="preserve">1 059 070</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 305</t>
+            <t xml:space="preserve">33 312</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 766</t>
+            <t xml:space="preserve">208 780</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 562</t>
+            <t xml:space="preserve">750 663</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 308</t>
+            <t xml:space="preserve">66 315</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 116</t>
+            <t xml:space="preserve">84 132</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 116</t>
+            <t xml:space="preserve">84 132</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46170.3202526737</v>
+        <v>46171.32026487263</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 050</t>
+            <t xml:space="preserve">3 570 030</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 145</t>
+            <t xml:space="preserve">464 221</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 058</t>
+            <t xml:space="preserve">145 075</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">781 030</t>
+            <t xml:space="preserve">780 976</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 492</t>
+            <t xml:space="preserve">1 136 433</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 073</t>
+            <t xml:space="preserve">547 085</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 271</t>
+            <t xml:space="preserve">309 251</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 811</t>
+            <t xml:space="preserve">84 827</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 170</t>
+            <t xml:space="preserve">102 162</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 583 929</t>
+            <t xml:space="preserve">1 584 054</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 667</t>
+            <t xml:space="preserve">1 204 736</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">220 068</t>
+            <t xml:space="preserve">220 116</t>
           </r>
         </is>
       </c>
@@ -549,7 +549,7 @@
       <c r="E14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.49</t>
+            <t xml:space="preserve">3.50</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 306</t>
+            <t xml:space="preserve">58 308</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 646</t>
+            <t xml:space="preserve">32 644</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 124</t>
+            <t xml:space="preserve">40 126</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 438</t>
+            <t xml:space="preserve">2 440</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 696</t>
+            <t xml:space="preserve">24 700</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 059 070</t>
+            <t xml:space="preserve">1 059 157</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 312</t>
+            <t xml:space="preserve">33 323</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 780</t>
+            <t xml:space="preserve">208 787</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 663</t>
+            <t xml:space="preserve">750 728</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 315</t>
+            <t xml:space="preserve">66 319</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 132</t>
+            <t xml:space="preserve">84 150</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 132</t>
+            <t xml:space="preserve">84 150</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46171.32026487263</v>
+        <v>46172.32024048595</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 030</t>
+            <t xml:space="preserve">3 570 035</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 221</t>
+            <t xml:space="preserve">464 249</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 075</t>
+            <t xml:space="preserve">145 081</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">780 976</t>
+            <t xml:space="preserve">780 957</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 433</t>
+            <t xml:space="preserve">1 136 409</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 085</t>
+            <t xml:space="preserve">547 096</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 251</t>
+            <t xml:space="preserve">309 253</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 827</t>
+            <t xml:space="preserve">84 830</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 162</t>
+            <t xml:space="preserve">102 160</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 584 054</t>
+            <t xml:space="preserve">1 584 104</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 736</t>
+            <t xml:space="preserve">1 204 762</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">220 116</t>
+            <t xml:space="preserve">220 137</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 308</t>
+            <t xml:space="preserve">58 311</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 644</t>
+            <t xml:space="preserve">32 643</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 126</t>
+            <t xml:space="preserve">40 125</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 700</t>
+            <t xml:space="preserve">24 702</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 059 157</t>
+            <t xml:space="preserve">1 059 203</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 323</t>
+            <t xml:space="preserve">33 325</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 787</t>
+            <t xml:space="preserve">208 796</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 728</t>
+            <t xml:space="preserve">750 764</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 319</t>
+            <t xml:space="preserve">66 318</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 150</t>
+            <t xml:space="preserve">84 189</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 150</t>
+            <t xml:space="preserve">84 189</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46172.32024048595</v>
+        <v>46174.32025300944</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 570 035</t>
+            <t xml:space="preserve">3 569 977</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 249</t>
+            <t xml:space="preserve">464 333</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 081</t>
+            <t xml:space="preserve">145 110</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">780 957</t>
+            <t xml:space="preserve">780 915</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 409</t>
+            <t xml:space="preserve">1 136 310</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.05</t>
+            <t xml:space="preserve">18.04</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 096</t>
+            <t xml:space="preserve">547 103</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 253</t>
+            <t xml:space="preserve">309 218</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 830</t>
+            <t xml:space="preserve">84 842</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 160</t>
+            <t xml:space="preserve">102 146</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 584 104</t>
+            <t xml:space="preserve">1 584 284</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.15</t>
+            <t xml:space="preserve">25.16</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 762</t>
+            <t xml:space="preserve">1 204 867</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">220 137</t>
+            <t xml:space="preserve">220 185</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 311</t>
+            <t xml:space="preserve">58 318</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 643</t>
+            <t xml:space="preserve">32 645</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 125</t>
+            <t xml:space="preserve">40 129</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 440</t>
+            <t xml:space="preserve">2 444</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 702</t>
+            <t xml:space="preserve">24 712</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 059 203</t>
+            <t xml:space="preserve">1 059 326</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 325</t>
+            <t xml:space="preserve">33 336</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 796</t>
+            <t xml:space="preserve">208 792</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 764</t>
+            <t xml:space="preserve">750 879</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 318</t>
+            <t xml:space="preserve">66 319</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 189</t>
+            <t xml:space="preserve">84 216</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 189</t>
+            <t xml:space="preserve">84 216</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46174.32025300944</v>
+        <v>46175.32024655072</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 977</t>
+            <t xml:space="preserve">3 569 282</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 333</t>
+            <t xml:space="preserve">463 721</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">145 110</t>
+            <t xml:space="preserve">143 577</t>
           </r>
         </is>
       </c>
@@ -315,7 +315,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2.30</t>
+            <t xml:space="preserve">2.28</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">780 915</t>
+            <t xml:space="preserve">776 891</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.40</t>
+            <t xml:space="preserve">12.34</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 136 310</t>
+            <t xml:space="preserve">1 137 856</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.04</t>
+            <t xml:space="preserve">18.07</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">547 103</t>
+            <t xml:space="preserve">643 250</t>
           </r>
         </is>
       </c>
@@ -393,7 +393,7 @@
       <c r="E8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">8.69</t>
+            <t xml:space="preserve">10.22</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">309 218</t>
+            <t xml:space="preserve">308 786</t>
           </r>
         </is>
       </c>
@@ -419,7 +419,7 @@
       <c r="E9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">4.91</t>
+            <t xml:space="preserve">4.90</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 842</t>
+            <t xml:space="preserve">88 499</t>
           </r>
         </is>
       </c>
@@ -445,7 +445,7 @@
       <c r="E10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.35</t>
+            <t xml:space="preserve">1.41</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">102 146</t>
+            <t xml:space="preserve">6 702</t>
           </r>
         </is>
       </c>
@@ -471,7 +471,7 @@
       <c r="E11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.62</t>
+            <t xml:space="preserve">0.11</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 584 284</t>
+            <t xml:space="preserve">1 588 543</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.16</t>
+            <t xml:space="preserve">25.23</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 204 867</t>
+            <t xml:space="preserve">1 206 504</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.13</t>
+            <t xml:space="preserve">19.16</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">220 185</t>
+            <t xml:space="preserve">222 619</t>
           </r>
         </is>
       </c>
@@ -549,7 +549,7 @@
       <c r="E14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.50</t>
+            <t xml:space="preserve">3.54</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 318</t>
+            <t xml:space="preserve">58 515</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 645</t>
+            <t xml:space="preserve">32 659</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 129</t>
+            <t xml:space="preserve">40 144</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">984</t>
+            <t xml:space="preserve">973</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 444</t>
+            <t xml:space="preserve">2 445</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 712</t>
+            <t xml:space="preserve">24 684</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 059 326</t>
+            <t xml:space="preserve">1 055 671</t>
           </r>
         </is>
       </c>
@@ -731,7 +731,7 @@
       <c r="E21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16.82</t>
+            <t xml:space="preserve">16.77</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 336</t>
+            <t xml:space="preserve">33 134</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">208 792</t>
+            <t xml:space="preserve">206 082</t>
           </r>
         </is>
       </c>
@@ -783,7 +783,7 @@
       <c r="E23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.32</t>
+            <t xml:space="preserve">3.27</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 879</t>
+            <t xml:space="preserve">750 978</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.92</t>
+            <t xml:space="preserve">11.93</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">66 319</t>
+            <t xml:space="preserve">65 477</t>
           </r>
         </is>
       </c>
@@ -835,7 +835,7 @@
       <c r="E25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.05</t>
+            <t xml:space="preserve">1.04</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 216</t>
+            <t xml:space="preserve">82 778</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.34</t>
+            <t xml:space="preserve">1.31</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">84 216</t>
+            <t xml:space="preserve">82 778</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.34</t>
+            <t xml:space="preserve">1.31</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46175.32024655072</v>
+        <v>46185.32025310164</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 282</t>
+            <t xml:space="preserve">3 569 227</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.69</t>
+            <t xml:space="preserve">56.68</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">463 721</t>
+            <t xml:space="preserve">463 936</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 577</t>
+            <t xml:space="preserve">143 638</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">776 891</t>
+            <t xml:space="preserve">776 770</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 137 856</t>
+            <t xml:space="preserve">1 137 669</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">643 250</t>
+            <t xml:space="preserve">643 263</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">308 786</t>
+            <t xml:space="preserve">308 728</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">88 499</t>
+            <t xml:space="preserve">88 521</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 588 543</t>
+            <t xml:space="preserve">1 588 885</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 206 504</t>
+            <t xml:space="preserve">1 206 714</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">222 619</t>
+            <t xml:space="preserve">222 735</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 515</t>
+            <t xml:space="preserve">58 519</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 659</t>
+            <t xml:space="preserve">32 655</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 144</t>
+            <t xml:space="preserve">40 150</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 445</t>
+            <t xml:space="preserve">2 447</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 684</t>
+            <t xml:space="preserve">24 692</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 055 671</t>
+            <t xml:space="preserve">1 055 941</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 134</t>
+            <t xml:space="preserve">33 161</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">206 082</t>
+            <t xml:space="preserve">206 088</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">750 978</t>
+            <t xml:space="preserve">751 205</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">65 477</t>
+            <t xml:space="preserve">65 487</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 778</t>
+            <t xml:space="preserve">82 822</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.31</t>
+            <t xml:space="preserve">1.32</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 778</t>
+            <t xml:space="preserve">82 822</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.31</t>
+            <t xml:space="preserve">1.32</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46185.32025310164</v>
+        <v>46189.32025462948</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 227</t>
+            <t xml:space="preserve">3 569 019</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.68</t>
+            <t xml:space="preserve">56.67</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">463 936</t>
+            <t xml:space="preserve">464 253</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 638</t>
+            <t xml:space="preserve">143 703</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">776 770</t>
+            <t xml:space="preserve">776 535</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.34</t>
+            <t xml:space="preserve">12.33</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 137 669</t>
+            <t xml:space="preserve">1 137 371</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.07</t>
+            <t xml:space="preserve">18.06</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">643 263</t>
+            <t xml:space="preserve">643 275</t>
           </r>
         </is>
       </c>
@@ -393,7 +393,7 @@
       <c r="E8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">10.22</t>
+            <t xml:space="preserve">10.21</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">308 728</t>
+            <t xml:space="preserve">308 625</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">88 521</t>
+            <t xml:space="preserve">88 557</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">6 702</t>
+            <t xml:space="preserve">6 700</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 588 885</t>
+            <t xml:space="preserve">1 589 372</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.23</t>
+            <t xml:space="preserve">25.24</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 206 714</t>
+            <t xml:space="preserve">1 207 016</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.16</t>
+            <t xml:space="preserve">19.17</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">222 735</t>
+            <t xml:space="preserve">222 878</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 519</t>
+            <t xml:space="preserve">58 537</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 655</t>
+            <t xml:space="preserve">32 654</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 150</t>
+            <t xml:space="preserve">40 157</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">973</t>
+            <t xml:space="preserve">974</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 447</t>
+            <t xml:space="preserve">2 449</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 692</t>
+            <t xml:space="preserve">24 707</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 055 941</t>
+            <t xml:space="preserve">1 056 297</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 161</t>
+            <t xml:space="preserve">33 205</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">206 088</t>
+            <t xml:space="preserve">206 072</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">751 205</t>
+            <t xml:space="preserve">751 511</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">65 487</t>
+            <t xml:space="preserve">65 509</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 822</t>
+            <t xml:space="preserve">82 913</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 822</t>
+            <t xml:space="preserve">82 913</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46189.32025462948</v>
+        <v>46192.32025190955</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 569 019</t>
+            <t xml:space="preserve">3 568 963</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 253</t>
+            <t xml:space="preserve">464 351</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 703</t>
+            <t xml:space="preserve">143 721</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">776 535</t>
+            <t xml:space="preserve">776 458</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 137 371</t>
+            <t xml:space="preserve">1 137 282</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">643 275</t>
+            <t xml:space="preserve">643 277</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">308 625</t>
+            <t xml:space="preserve">308 600</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">88 557</t>
+            <t xml:space="preserve">88 574</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 589 372</t>
+            <t xml:space="preserve">1 589 567</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 207 016</t>
+            <t xml:space="preserve">1 207 141</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">222 878</t>
+            <t xml:space="preserve">222 923</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 537</t>
+            <t xml:space="preserve">58 543</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 654</t>
+            <t xml:space="preserve">32 651</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 157</t>
+            <t xml:space="preserve">40 170</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">974</t>
+            <t xml:space="preserve">973</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 707</t>
+            <t xml:space="preserve">24 717</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 056 297</t>
+            <t xml:space="preserve">1 056 424</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 205</t>
+            <t xml:space="preserve">33 211</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">206 072</t>
+            <t xml:space="preserve">206 082</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">751 511</t>
+            <t xml:space="preserve">751 620</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">65 509</t>
+            <t xml:space="preserve">65 511</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 913</t>
+            <t xml:space="preserve">82 931</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 913</t>
+            <t xml:space="preserve">82 931</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46192.32025190955</v>
+        <v>46204.32026256947</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46204.32026256947</v>
+        <v>46211.32024581032</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46211.32024581032</v>
+        <v>46219.32024322916</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46219.32024322916</v>
+        <v>46220.320228646044</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46220.320228646044</v>
+        <v>46222.320236724336</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46222.320236724336</v>
+        <v>46224.32025203714</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46224.32025203714</v>
+        <v>46225.32025962975</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46225.32025962975</v>
+        <v>46231.32025490748</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46231.32025490748</v>
+        <v>46233.32025187509</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46233.32025187509</v>
+        <v>46235.32025087951</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46235.32025087951</v>
+        <v>46236.320270752534</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46236.320270752534</v>
+        <v>46237.3202361688</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46237.3202361688</v>
+        <v>46238.32024423592</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46238.32024423592</v>
+        <v>46240.32024651626</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46240.32024651626</v>
+        <v>46252.32025594916</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -255,7 +255,7 @@
       <c r="C3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3 568 963</t>
+            <t xml:space="preserve">3 567 078</t>
           </r>
         </is>
       </c>
@@ -263,7 +263,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">56.67</t>
+            <t xml:space="preserve">56.53</t>
           </r>
         </is>
       </c>
@@ -281,7 +281,7 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">464 351</t>
+            <t xml:space="preserve">468 450</t>
           </r>
         </is>
       </c>
@@ -289,7 +289,7 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">7.37</t>
+            <t xml:space="preserve">7.42</t>
           </r>
         </is>
       </c>
@@ -307,7 +307,7 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">143 721</t>
+            <t xml:space="preserve">144 584</t>
           </r>
         </is>
       </c>
@@ -315,7 +315,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2.28</t>
+            <t xml:space="preserve">2.29</t>
           </r>
         </is>
       </c>
@@ -333,7 +333,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">776 458</t>
+            <t xml:space="preserve">773 131</t>
           </r>
         </is>
       </c>
@@ -341,7 +341,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12.33</t>
+            <t xml:space="preserve">12.25</t>
           </r>
         </is>
       </c>
@@ -359,7 +359,7 @@
       <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 137 282</t>
+            <t xml:space="preserve">1 134 117</t>
           </r>
         </is>
       </c>
@@ -367,7 +367,7 @@
       <c r="E7" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18.06</t>
+            <t xml:space="preserve">17.97</t>
           </r>
         </is>
       </c>
@@ -385,7 +385,7 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">643 277</t>
+            <t xml:space="preserve">643 525</t>
           </r>
         </is>
       </c>
@@ -393,7 +393,7 @@
       <c r="E8" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">10.21</t>
+            <t xml:space="preserve">10.20</t>
           </r>
         </is>
       </c>
@@ -411,7 +411,7 @@
       <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">308 600</t>
+            <t xml:space="preserve">307 416</t>
           </r>
         </is>
       </c>
@@ -419,7 +419,7 @@
       <c r="E9" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">4.90</t>
+            <t xml:space="preserve">4.87</t>
           </r>
         </is>
       </c>
@@ -437,7 +437,7 @@
       <c r="C10" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">88 574</t>
+            <t xml:space="preserve">89 200</t>
           </r>
         </is>
       </c>
@@ -463,7 +463,7 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">6 700</t>
+            <t xml:space="preserve">6 655</t>
           </r>
         </is>
       </c>
@@ -489,7 +489,7 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 589 567</t>
+            <t xml:space="preserve">1 596 502</t>
           </r>
         </is>
       </c>
@@ -497,7 +497,7 @@
       <c r="E12" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">25.24</t>
+            <t xml:space="preserve">25.30</t>
           </r>
         </is>
       </c>
@@ -515,7 +515,7 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 207 141</t>
+            <t xml:space="preserve">1 211 444</t>
           </r>
         </is>
       </c>
@@ -523,7 +523,7 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">19.17</t>
+            <t xml:space="preserve">19.20</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">222 923</t>
+            <t xml:space="preserve">224 900</t>
           </r>
         </is>
       </c>
@@ -549,7 +549,7 @@
       <c r="E14" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">3.54</t>
+            <t xml:space="preserve">3.56</t>
           </r>
         </is>
       </c>
@@ -567,7 +567,7 @@
       <c r="C15" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">58 543</t>
+            <t xml:space="preserve">58 790</t>
           </r>
         </is>
       </c>
@@ -593,7 +593,7 @@
       <c r="C16" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32 651</t>
+            <t xml:space="preserve">32 632</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="C17" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">40 170</t>
+            <t xml:space="preserve">40 322</t>
           </r>
         </is>
       </c>
@@ -645,7 +645,7 @@
       <c r="C18" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">973</t>
+            <t xml:space="preserve">977</t>
           </r>
         </is>
       </c>
@@ -671,7 +671,7 @@
       <c r="C19" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2 449</t>
+            <t xml:space="preserve">2 475</t>
           </r>
         </is>
       </c>
@@ -697,7 +697,7 @@
       <c r="C20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">24 717</t>
+            <t xml:space="preserve">24 962</t>
           </r>
         </is>
       </c>
@@ -705,7 +705,7 @@
       <c r="E20" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">0.39</t>
+            <t xml:space="preserve">0.40</t>
           </r>
         </is>
       </c>
@@ -723,7 +723,7 @@
       <c r="C21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1 056 424</t>
+            <t xml:space="preserve">1 061 987</t>
           </r>
         </is>
       </c>
@@ -731,7 +731,7 @@
       <c r="E21" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16.77</t>
+            <t xml:space="preserve">16.83</t>
           </r>
         </is>
       </c>
@@ -749,7 +749,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">33 211</t>
+            <t xml:space="preserve">33 718</t>
           </r>
         </is>
       </c>
@@ -775,7 +775,7 @@
       <c r="C23" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">206 082</t>
+            <t xml:space="preserve">206 410</t>
           </r>
         </is>
       </c>
@@ -801,7 +801,7 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">751 620</t>
+            <t xml:space="preserve">756 187</t>
           </r>
         </is>
       </c>
@@ -809,7 +809,7 @@
       <c r="E24" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">11.93</t>
+            <t xml:space="preserve">11.98</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="C25" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">65 511</t>
+            <t xml:space="preserve">65 672</t>
           </r>
         </is>
       </c>
@@ -845,7 +845,7 @@
       <c r="A26" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
+            <t xml:space="preserve">Dane do weryfikacji</t>
           </r>
         </is>
       </c>
@@ -853,7 +853,7 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 931</t>
+            <t xml:space="preserve">84 516</t>
           </r>
         </is>
       </c>
@@ -861,7 +861,7 @@
       <c r="E26" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.32</t>
+            <t xml:space="preserve">1.34</t>
           </r>
         </is>
       </c>
@@ -871,7 +871,7 @@
       <c r="A27" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Dane do weryfikacji</t>
+            <t xml:space="preserve">DANE DO WERYFIKACJI</t>
           </r>
         </is>
       </c>
@@ -879,7 +879,7 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">82 931</t>
+            <t xml:space="preserve">84 516</t>
           </r>
         </is>
       </c>
@@ -887,7 +887,7 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1.32</t>
+            <t xml:space="preserve">1.34</t>
           </r>
         </is>
       </c>
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46252.32025594916</v>
+        <v>46253.32026248844</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46253.32026248844</v>
+        <v>46255.32024601847</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46255.32024601847</v>
+        <v>46256.32025156263</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46256.32025156263</v>
+        <v>46258.32025772007</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46258.32025772007</v>
+        <v>46261.32024635421</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46261.32024635421</v>
+        <v>46262.320245624986</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46262.320245624986</v>
+        <v>46264.320253911894</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46264.320253911894</v>
+        <v>46268.32025059033</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46268.32025059033</v>
+        <v>46269.320240694564</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>
